--- a/Treinamento/Index/Relatório de Recusas 26.01.2026 a 01.02.2026.xlsx
+++ b/Treinamento/Index/Relatório de Recusas 26.01.2026 a 01.02.2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/shirlei_witkowski_allianz_com_br/Documents/Planilha de recusa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{671137DB-1C50-4294-A4DC-5A512359DA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5AA5D6A-A45B-4E2B-8034-D9CE678CD41A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26.01" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="231">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -637,7 +637,280 @@
     <t>Não</t>
   </si>
   <si>
-    <t>28.01</t>
+    <t xml:space="preserve">CRISTIANO DE ARRUDA BARBIRATO                </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 27.01.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO APARECIDO STUCHI                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ROBERTO PEREIRA DE OLIVEIRA            </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do pass, Traseira e lateral do mot, Painel, Porta malas, Documento, Chassi, Frente e lateral do mot, Motor, Traseira e lateral do pass.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO CASTILHO DE BIASI                   </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENILDA SILVA ALMEIDA                        </t>
+  </si>
+  <si>
+    <t>RECUSA: *PRAZO EXPIRADO * repique: Painel com a motocicleta ligada / tanque comb risc; 1 frente risc; 1 pr para-lama diant risc; 1 pt escap risc; 1 pt lat dir risc; 1 pt alça risc; 1 pt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA MAYARA PEREIRA DA SILVA DIAS           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">D B TRANSPORTE RODOVIARIO DE CARGAS LTDA ME  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JACQUELINE SALES DE LIMA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURIPEDES FERREIRA AMORIM                    </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Frente e lateral do passageiro, Traseira e lateral do motorista, Frente e lateral do motorista, Traseira e lateral do passageiro (Foto não enquadrada corretamente), Documento do veículo (Foto embaçada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDGARD TEIXEIRA DE MELLO NETO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARILENE TORQUATO SILVA                      </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro, Painel com carro ligado, Documento do veículo, Frente e lateral do motorista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLAN DE OLIVEIRA CAMPOS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORMA SANTANA ALMEIDA                        </t>
+  </si>
+  <si>
+    <t>RECUSA: SEGURADO NÃO REFEZ A FOTO DO CHASSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSANGELA SOUZA DE ALMEIDA FERREIRA          </t>
+  </si>
+  <si>
+    <t>Conforme CBE houve sinistro na apólice anterior, portanto a renova
+ção correta é externa COM sinistro, conforme regra diminui uma cla
+sse debônus, assim sendo o correto bônus “08“.
+Com a correção
+ficou 10x R$ 641,64. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ANTONIO MORELLI                         </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que
+a apólice consta ativa na congênere, para que possamos prossegui
+r coma liberação do bloqueio será necessário a apresentação do e
+ndosso de cancelamento emitido, a atualização junto a Central de B
+ônus.</t>
+  </si>
+  <si>
+    <t>PAO DE ACUCAR ALIMENTOS ATACADO VAREJO LTDA M</t>
+  </si>
+  <si>
+    <t>RECUSA: *PRAZO EXPIRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS repique: Chassi // DISJUNTOR INSTALADO NO MOTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HENRIQUE ZORZETTI                            </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:
+– Cópia da apólice congênere c
+om vigência de 2026 a 2027.
+– Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO TEODORO DA SILVA NETO                   </t>
+  </si>
+  <si>
+    <t>C
+onforme regra de apólices canceladas houve quebra de vigência de 3
+65 dias ou mais, portanto devem-se excluir todas as classes de bôn
+us e considerar como seguro novo.
+Com a correção ficou 10x R$ 2
+36,19. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASSIA MARIA MARQUES DE SOUZA LIMA           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSEFA FERREIRA AMORIM                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERIKA SAYURI MATUMOTO ONO                    </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE não houve sinistro na apólice anterior, conforme regra
+é concedida uma classe de bônus, assim sendo, apólice anterior ti
+nha classe de bônus 6 o correto passa à ser bônus “ 7 “.
+Com a correção ficou 1x R$ 1.443,23. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE ROBERTO DA SILVA                        </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:
+– Cópia da apólice congênere c
+om vigência de 2026 a 2027. Endosso de cancelamento emitido.
+PENDÊNCIA 1736 – DIVERGÊNCIAS CBE (Divergência de bônus).
+Conforme CBE não houve sinistro na apólice anterior, conforme
+regra é concedida uma classe de bônus, assim sendo, apólice anter
+ior tinha classe de bônus 0 o correto passa à ser bônus “ 1 “.
+Com a correção ficou10x R$ 478,24. Podemos emitir desta for
+ma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEBORA FAZENDEIRO PINTO SILVA                </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE trata-se de renovação congênere sendo renovada com 46
+dias em atraso e não houve sinistro , conforme regra mantem a cla
+sse debônus, assim sendo o correto bônus 1.
+Com a correção fico
+u 10x R$ 477,39. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRLEIA DE SOUZA GOMES                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCO ANTONIO DE AGUIAR COUTO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade efetuar a transferência de bônus para o(a) senhor(a) M
+ARCOANTONIO DE AGUIAR COUTO, pois este não consta como condutor na
+apólice anterior.
+Neste caso, iremos realizar a recusa d
+esta proposta, para conclusão do processo é necessário informar o
+email dosegurado anterior (LUCIENE MARQUES DA COSTA), para que o m
+esmo também fique ciente da recusa. do segurado anterior (MARKSON
+VIDAL SANTOS), para que o mesmo também fique ciente da recusa.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FERNANDA CARRIAO RIBEIRO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C
+onforme CBE não houve sinistro na apólice anterior, conforme regra
+é concedida uma classe de bônus, assim sendo, apólice anterior ti
+nha classe de bônus 0 o correto passa à ser bônus “ 2 “.
+Com a correção ficou 10x R$ 215,53. Podemos emitir desta forma?.........
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAX GUILHERME DE ANDRADE E SILVA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGDA PONTIN VIGANO                          </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE não houve sinistro na apólice anterior, conforme regra
+é concedida uma classe de bônus, assim sendo, apólice anterior ti
+nha classe de bônus 4 o correto passa à ser bônus “ 5 “.
+Com a correção ficou 10x R$ 243,85. Podemos emitir desta forma?..</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA CELIA DA COSTA BOBBIO MILANEZ          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEMIR DE SOUZA MUNIZ                        </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:
+– Cópia da apólice congênere c
+om vigência de 2026 a 2027.
+- Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DONIZETE APARECIDO VISMAR                    </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:
+– Cópia da apólice congênere c
+om vigência de 2025 a 2026.
+– Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEILTON MARCELO CARVALHO DE OLIVEIRA        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANILTON JOSE MATURINO DOS SANTOS             </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não há po
+ssibilidade efetuar a transferência de bônus para o(a) senhor(a) A
+NILTON JOSE MATURINO DOS SANTOS, pois este não consta no quadro so
+cietário da empresa/segurado anterior REAL COMERCIO DE PRODUTOS FA
+LTDA.
+Neste caso, iremos realizar a recusa desta proposta
+, para conclusão do processo é necessário informar o email do segu
+rado anterior (REAL COMERCIO DE PRODUTOS FA LTDA), para que o mesm
+o também fique ciente da recusa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE LINHARES MARQUES                        </t>
+  </si>
+  <si>
+    <t>I
+dentificamos que a proposta foi transmitida com bônus 7, conforme
+CBE bonificação está incorreta, apólice anterior consta classe de
+bônus7, não havendo sinistro, conforme regra concede 1 classe de b
+ônus, assim sendo o correto bônus 8.
+Com a correção ficou 10x
+R$ 413,44. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONIQUE DE OLIVEIRA BERNARDINO               </t>
+  </si>
+  <si>
+    <t>Veículo informado é diferente do calculado
+Constatamos que o modelo do veículo informado na cotação difere d
+o constado, segue abaixo informação retornada pelo sistema através
+do chassi do veículo:
+Modelo constatado: VOLKSWAGEN FOX
+Trendline 1.6 MSI Total Flex 4p
+FIPE: 005406-2
+Valor do prê
+mio: 10x R$ 225,27
+Franquia: R$ 3.013,47
+Podemos emitir
+dessa forma?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA ISABEL DO AMARAL PINTO NUNES           </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Documento do veículo, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KELLY PEREIRA DE MOURA                       </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Traseira e lateral do motorista</t>
   </si>
 </sst>
 </file>
@@ -702,7 +975,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -878,17 +1151,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -897,17 +1159,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1001,7 +1252,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1052,9 +1303,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1160,9 +1408,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1170,21 +1415,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1198,37 +1433,57 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1608,72 +1863,72 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="76" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="75" t="s">
+      <c r="A2" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="64">
+      <c r="E2" s="62">
         <v>3450213866</v>
       </c>
-      <c r="F2" s="80" t="s">
+      <c r="F2" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="45" t="s">
+      <c r="H2" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="43" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="76" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="75" t="s">
+      <c r="A3" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="77">
+      <c r="C3" s="71">
         <v>46048</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="17">
         <v>3450228287</v>
       </c>
-      <c r="F3" s="74" t="s">
+      <c r="F3" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="78" t="s">
+      <c r="G3" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="45" t="s">
+      <c r="H3" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="44"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="55">
+      <c r="B4" s="54">
         <v>46037</v>
       </c>
-      <c r="C4" s="77">
+      <c r="C4" s="71">
         <v>46048</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>136212396</v>
       </c>
       <c r="E4" s="17">
@@ -1682,13 +1937,13 @@
       <c r="F4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="78" t="s">
+      <c r="G4" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="45" t="s">
+      <c r="H4" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -1699,10 +1954,10 @@
       <c r="B5" s="7">
         <v>46035</v>
       </c>
-      <c r="C5" s="77">
+      <c r="C5" s="71">
         <v>46048</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="21">
         <v>136220387</v>
       </c>
       <c r="E5" s="17">
@@ -1711,13 +1966,13 @@
       <c r="F5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="78" t="s">
+      <c r="G5" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="45" t="s">
+      <c r="H5" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="43">
         <v>46045</v>
       </c>
     </row>
@@ -1728,10 +1983,10 @@
       <c r="B6" s="7">
         <v>46038</v>
       </c>
-      <c r="C6" s="77">
+      <c r="C6" s="71">
         <v>46048</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>136227830</v>
       </c>
       <c r="E6" s="17">
@@ -1740,13 +1995,13 @@
       <c r="F6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="78" t="s">
+      <c r="G6" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -1757,10 +2012,10 @@
       <c r="B7" s="7">
         <v>46036</v>
       </c>
-      <c r="C7" s="77">
+      <c r="C7" s="71">
         <v>46048</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>136228192</v>
       </c>
       <c r="E7" s="17">
@@ -1769,13 +2024,13 @@
       <c r="F7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="78" t="s">
+      <c r="G7" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="46" t="s">
+      <c r="H7" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="43">
         <v>46044</v>
       </c>
     </row>
@@ -1786,10 +2041,10 @@
       <c r="B8" s="7">
         <v>46057</v>
       </c>
-      <c r="C8" s="77">
+      <c r="C8" s="71">
         <v>46048</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>136230170</v>
       </c>
       <c r="E8" s="17">
@@ -1798,13 +2053,13 @@
       <c r="F8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="78" t="s">
+      <c r="G8" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="46" t="s">
+      <c r="H8" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -1815,10 +2070,10 @@
       <c r="B9" s="7">
         <v>46065</v>
       </c>
-      <c r="C9" s="77">
+      <c r="C9" s="71">
         <v>46048</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>136230598</v>
       </c>
       <c r="E9" s="17">
@@ -1827,13 +2082,13 @@
       <c r="F9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="78" t="s">
+      <c r="G9" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -1844,10 +2099,10 @@
       <c r="B10" s="7">
         <v>46037</v>
       </c>
-      <c r="C10" s="77">
+      <c r="C10" s="71">
         <v>46048</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>136255805</v>
       </c>
       <c r="E10" s="17">
@@ -1856,13 +2111,13 @@
       <c r="F10" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="78" t="s">
+      <c r="G10" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -1873,10 +2128,10 @@
       <c r="B11" s="7">
         <v>46037</v>
       </c>
-      <c r="C11" s="77">
+      <c r="C11" s="71">
         <v>46048</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <v>136259591</v>
       </c>
       <c r="E11" s="17">
@@ -1885,13 +2140,13 @@
       <c r="F11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="78" t="s">
+      <c r="G11" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="45" t="s">
+      <c r="H11" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -1902,10 +2157,10 @@
       <c r="B12" s="7">
         <v>46050</v>
       </c>
-      <c r="C12" s="77">
+      <c r="C12" s="71">
         <v>46048</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>136216099</v>
       </c>
       <c r="E12" s="17">
@@ -1914,13 +2169,13 @@
       <c r="F12" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="78" t="s">
+      <c r="G12" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="45" t="s">
+      <c r="H12" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -1931,10 +2186,10 @@
       <c r="B13" s="7">
         <v>46066</v>
       </c>
-      <c r="C13" s="77">
+      <c r="C13" s="71">
         <v>46048</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>136300559</v>
       </c>
       <c r="E13" s="17">
@@ -1943,13 +2198,13 @@
       <c r="F13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G13" s="78" t="s">
+      <c r="G13" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="45" t="s">
+      <c r="H13" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>46045</v>
       </c>
     </row>
@@ -1960,10 +2215,10 @@
       <c r="B14" s="7">
         <v>46041</v>
       </c>
-      <c r="C14" s="77">
+      <c r="C14" s="71">
         <v>46048</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>136302684</v>
       </c>
       <c r="E14" s="17">
@@ -1972,13 +2227,13 @@
       <c r="F14" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="78" t="s">
+      <c r="G14" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="43">
         <v>46045</v>
       </c>
     </row>
@@ -1989,10 +2244,10 @@
       <c r="B15" s="7">
         <v>46041</v>
       </c>
-      <c r="C15" s="77">
+      <c r="C15" s="71">
         <v>46048</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>136306186</v>
       </c>
       <c r="E15" s="17">
@@ -2001,13 +2256,13 @@
       <c r="F15" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="78" t="s">
+      <c r="G15" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="45" t="s">
+      <c r="H15" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -2018,10 +2273,10 @@
       <c r="B16" s="7">
         <v>46041</v>
       </c>
-      <c r="C16" s="77">
+      <c r="C16" s="71">
         <v>46048</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <v>136308029</v>
       </c>
       <c r="E16" s="17">
@@ -2030,13 +2285,13 @@
       <c r="F16" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="78" t="s">
+      <c r="G16" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="H16" s="45" t="s">
+      <c r="H16" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -2047,10 +2302,10 @@
       <c r="B17" s="7">
         <v>46041</v>
       </c>
-      <c r="C17" s="77">
+      <c r="C17" s="71">
         <v>46048</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>136318258</v>
       </c>
       <c r="E17" s="17">
@@ -2059,13 +2314,13 @@
       <c r="F17" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="78" t="s">
+      <c r="G17" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="45" t="s">
+      <c r="H17" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -2076,10 +2331,10 @@
       <c r="B18" s="7">
         <v>46041</v>
       </c>
-      <c r="C18" s="77">
+      <c r="C18" s="71">
         <v>46048</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>136322481</v>
       </c>
       <c r="E18" s="17">
@@ -2088,13 +2343,13 @@
       <c r="F18" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="78" t="s">
+      <c r="G18" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -2105,10 +2360,10 @@
       <c r="B19" s="7">
         <v>46041</v>
       </c>
-      <c r="C19" s="77">
+      <c r="C19" s="71">
         <v>46048</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>136305826</v>
       </c>
       <c r="E19" s="17">
@@ -2117,13 +2372,13 @@
       <c r="F19" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="78" t="s">
+      <c r="G19" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="H19" s="45" t="s">
+      <c r="H19" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="43">
         <v>46045</v>
       </c>
     </row>
@@ -2134,10 +2389,10 @@
       <c r="B20" s="7">
         <v>46042</v>
       </c>
-      <c r="C20" s="77">
+      <c r="C20" s="71">
         <v>46048</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <v>136333509</v>
       </c>
       <c r="E20" s="17">
@@ -2146,13 +2401,13 @@
       <c r="F20" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G20" s="78" t="s">
+      <c r="G20" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="H20" s="45" t="s">
+      <c r="H20" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -2163,10 +2418,10 @@
       <c r="B21" s="7">
         <v>46041</v>
       </c>
-      <c r="C21" s="77">
+      <c r="C21" s="71">
         <v>46048</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="21">
         <v>136304716</v>
       </c>
       <c r="E21" s="17">
@@ -2175,13 +2430,13 @@
       <c r="F21" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="G21" s="78" t="s">
+      <c r="G21" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="H21" s="45" t="s">
+      <c r="H21" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -2192,10 +2447,10 @@
       <c r="B22" s="7">
         <v>46041</v>
       </c>
-      <c r="C22" s="77">
+      <c r="C22" s="71">
         <v>46048</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <v>136315367</v>
       </c>
       <c r="E22" s="17">
@@ -2204,13 +2459,13 @@
       <c r="F22" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G22" s="78" t="s">
+      <c r="G22" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="H22" s="45" t="s">
+      <c r="H22" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -2221,10 +2476,10 @@
       <c r="B23" s="7">
         <v>46042</v>
       </c>
-      <c r="C23" s="77">
+      <c r="C23" s="71">
         <v>46048</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <v>136328002</v>
       </c>
       <c r="E23" s="17">
@@ -2233,13 +2488,13 @@
       <c r="F23" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G23" s="78" t="s">
+      <c r="G23" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="H23" s="45" t="s">
+      <c r="H23" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -2250,10 +2505,10 @@
       <c r="B24" s="7">
         <v>46042</v>
       </c>
-      <c r="C24" s="77">
+      <c r="C24" s="71">
         <v>46048</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <v>136338477</v>
       </c>
       <c r="E24" s="17">
@@ -2262,13 +2517,13 @@
       <c r="F24" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G24" s="78" t="s">
+      <c r="G24" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="H24" s="45" t="s">
+      <c r="H24" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -2279,10 +2534,10 @@
       <c r="B25" s="7">
         <v>46042</v>
       </c>
-      <c r="C25" s="77">
+      <c r="C25" s="71">
         <v>46048</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <v>136335272</v>
       </c>
       <c r="E25" s="17">
@@ -2291,13 +2546,13 @@
       <c r="F25" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="78" t="s">
+      <c r="G25" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="H25" s="45" t="s">
+      <c r="H25" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -2308,10 +2563,10 @@
       <c r="B26" s="7">
         <v>46043</v>
       </c>
-      <c r="C26" s="77">
+      <c r="C26" s="71">
         <v>46048</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <v>136354445</v>
       </c>
       <c r="E26" s="17">
@@ -2320,13 +2575,13 @@
       <c r="F26" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G26" s="78" t="s">
+      <c r="G26" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="H26" s="45" t="s">
+      <c r="H26" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -2337,10 +2592,10 @@
       <c r="B27" s="7">
         <v>46041</v>
       </c>
-      <c r="C27" s="77">
+      <c r="C27" s="71">
         <v>46048</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <v>136308579</v>
       </c>
       <c r="E27" s="17">
@@ -2349,13 +2604,13 @@
       <c r="F27" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G27" s="78" t="s">
+      <c r="G27" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="H27" s="45" t="s">
+      <c r="H27" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="43">
         <v>46045</v>
       </c>
     </row>
@@ -2366,10 +2621,10 @@
       <c r="B28" s="7">
         <v>46044</v>
       </c>
-      <c r="C28" s="84">
+      <c r="C28" s="78">
         <v>46048</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <v>136360372</v>
       </c>
       <c r="E28" s="17">
@@ -2378,13 +2633,13 @@
       <c r="F28" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G28" s="78" t="s">
+      <c r="G28" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="H28" s="45" t="s">
+      <c r="H28" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="43">
         <v>46044</v>
       </c>
     </row>
@@ -2392,13 +2647,13 @@
       <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="47">
+      <c r="B29" s="46">
         <v>46045</v>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="43">
         <v>46048</v>
       </c>
-      <c r="D29" s="83">
+      <c r="D29" s="77">
         <v>136394438</v>
       </c>
       <c r="E29" s="17">
@@ -2407,13 +2662,13 @@
       <c r="F29" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G29" s="78" t="s">
+      <c r="G29" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="H29" s="45" t="s">
+      <c r="H29" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="43">
         <v>46045</v>
       </c>
     </row>
@@ -2424,10 +2679,10 @@
       <c r="B30" s="7">
         <v>46047</v>
       </c>
-      <c r="C30" s="85">
+      <c r="C30" s="79">
         <v>46048</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="21">
         <v>136400551</v>
       </c>
       <c r="E30" s="17">
@@ -2436,13 +2691,13 @@
       <c r="F30" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G30" s="78" t="s">
+      <c r="G30" s="72" t="s">
         <v>69</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="43">
         <v>46047</v>
       </c>
     </row>
@@ -2453,10 +2708,10 @@
       <c r="B31" s="7">
         <v>46034</v>
       </c>
-      <c r="C31" s="77">
+      <c r="C31" s="71">
         <v>46048</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="21">
         <v>136198975</v>
       </c>
       <c r="E31" s="17">
@@ -2465,13 +2720,13 @@
       <c r="F31" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G31" s="78" t="s">
+      <c r="G31" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -2482,10 +2737,10 @@
       <c r="B32" s="7">
         <v>46048</v>
       </c>
-      <c r="C32" s="77">
+      <c r="C32" s="71">
         <v>46048</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="21">
         <v>136225295</v>
       </c>
       <c r="E32" s="17">
@@ -2494,13 +2749,13 @@
       <c r="F32" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="G32" s="78" t="s">
+      <c r="G32" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -2511,10 +2766,10 @@
       <c r="B33" s="7">
         <v>46041</v>
       </c>
-      <c r="C33" s="77">
+      <c r="C33" s="71">
         <v>46048</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="21">
         <v>136313592</v>
       </c>
       <c r="E33" s="17">
@@ -2523,13 +2778,13 @@
       <c r="F33" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G33" s="78" t="s">
+      <c r="G33" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -2540,10 +2795,10 @@
       <c r="B34" s="7">
         <v>46035</v>
       </c>
-      <c r="C34" s="77">
+      <c r="C34" s="71">
         <v>46048</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="21">
         <v>136231084</v>
       </c>
       <c r="E34" s="17">
@@ -2552,13 +2807,13 @@
       <c r="F34" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G34" s="78" t="s">
+      <c r="G34" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -2569,10 +2824,10 @@
       <c r="B35" s="7">
         <v>46037</v>
       </c>
-      <c r="C35" s="77">
+      <c r="C35" s="71">
         <v>46048</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="21">
         <v>136263397</v>
       </c>
       <c r="E35" s="17">
@@ -2581,13 +2836,13 @@
       <c r="F35" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G35" s="78" t="s">
+      <c r="G35" s="72" t="s">
         <v>24</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -2598,10 +2853,10 @@
       <c r="B36" s="7">
         <v>46042</v>
       </c>
-      <c r="C36" s="77">
+      <c r="C36" s="71">
         <v>46048</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="21">
         <v>136325831</v>
       </c>
       <c r="E36" s="17">
@@ -2610,13 +2865,13 @@
       <c r="F36" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="G36" s="78" t="s">
+      <c r="G36" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -2627,10 +2882,10 @@
       <c r="B37" s="7">
         <v>46041</v>
       </c>
-      <c r="C37" s="77">
+      <c r="C37" s="71">
         <v>46048</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="21">
         <v>136318119</v>
       </c>
       <c r="E37" s="17">
@@ -2639,13 +2894,13 @@
       <c r="F37" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G37" s="78" t="s">
+      <c r="G37" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -2656,10 +2911,10 @@
       <c r="B38" s="7">
         <v>46043</v>
       </c>
-      <c r="C38" s="77">
+      <c r="C38" s="71">
         <v>46048</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="21">
         <v>136221382</v>
       </c>
       <c r="E38" s="17">
@@ -2668,37 +2923,37 @@
       <c r="F38" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="78" t="s">
+      <c r="G38" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="I38" s="44">
+      <c r="I38" s="43">
         <v>46038</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="81"/>
-      <c r="E39" s="57"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="42"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="75"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="41"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="44"/>
+      <c r="I39" s="43"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="43"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="42"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="42"/>
+      <c r="G40" s="41"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="49"/>
+      <c r="I40" s="48"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
@@ -2708,7 +2963,7 @@
       <c r="E41" s="8"/>
       <c r="F41" s="9"/>
       <c r="G41" s="6"/>
-      <c r="H41" s="48"/>
+      <c r="H41" s="47"/>
       <c r="I41" s="12"/>
     </row>
   </sheetData>
@@ -2746,60 +3001,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="53" t="s">
+      <c r="E1" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="50" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="55" t="s">
+      <c r="A2" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="57">
+      <c r="E2" s="56">
         <v>3450223700</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="58" t="s">
+      <c r="G2" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="59" t="s">
+      <c r="I2" s="58" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2810,25 +3065,25 @@
       <c r="B3" s="7">
         <v>46048</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="57">
+      <c r="E3" s="56">
         <v>3450229960</v>
       </c>
-      <c r="F3" s="65" t="s">
+      <c r="F3" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="82" t="s">
+      <c r="H3" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="44"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -2837,25 +3092,25 @@
       <c r="B4" s="7">
         <v>46037</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>136260706</v>
       </c>
-      <c r="E4" s="87">
+      <c r="E4" s="81">
         <v>3450218673</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G4" s="78" t="s">
+      <c r="G4" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="44">
+      <c r="I4" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -2866,25 +3121,25 @@
       <c r="B5" s="7">
         <v>46036</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="21">
         <v>136260477</v>
       </c>
-      <c r="E5" s="87">
+      <c r="E5" s="81">
         <v>3450217034</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G5" s="78" t="s">
+      <c r="G5" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -2895,25 +3150,25 @@
       <c r="B6" s="7">
         <v>46036</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>136242732</v>
       </c>
-      <c r="E6" s="87">
+      <c r="E6" s="81">
         <v>3450217364</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="G6" s="78" t="s">
+      <c r="G6" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="44">
+      <c r="I6" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -2924,25 +3179,25 @@
       <c r="B7" s="7">
         <v>46038</v>
       </c>
-      <c r="C7" s="56" t="s">
+      <c r="C7" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>136287697</v>
       </c>
-      <c r="E7" s="87">
+      <c r="E7" s="81">
         <v>3450220807</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="78" t="s">
+      <c r="G7" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -2953,25 +3208,25 @@
       <c r="B8" s="7">
         <v>46038</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>136292249</v>
       </c>
-      <c r="E8" s="87">
+      <c r="E8" s="81">
         <v>3450221170</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G8" s="78" t="s">
+      <c r="G8" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="44">
+      <c r="I8" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -2982,25 +3237,25 @@
       <c r="B9" s="7">
         <v>46037</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>136273270</v>
       </c>
-      <c r="E9" s="87">
+      <c r="E9" s="81">
         <v>3450219950</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G9" s="78" t="s">
+      <c r="G9" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="44">
+      <c r="I9" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3011,25 +3266,25 @@
       <c r="B10" s="7">
         <v>46038</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>136287593</v>
       </c>
-      <c r="E10" s="87">
+      <c r="E10" s="81">
         <v>3450220785</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G10" s="78" t="s">
+      <c r="G10" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="I10" s="44">
+      <c r="I10" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -3040,25 +3295,25 @@
       <c r="B11" s="7">
         <v>46041</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <v>136340803</v>
       </c>
-      <c r="E11" s="87">
+      <c r="E11" s="81">
         <v>3450222061</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G11" s="78" t="s">
+      <c r="G11" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="I11" s="44">
+      <c r="I11" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -3069,25 +3324,25 @@
       <c r="B12" s="7">
         <v>46043</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>136347294</v>
       </c>
-      <c r="E12" s="87">
+      <c r="E12" s="81">
         <v>3450224790</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="78" t="s">
+      <c r="G12" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3098,25 +3353,25 @@
       <c r="B13" s="7">
         <v>46043</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>136348208</v>
       </c>
-      <c r="E13" s="87">
+      <c r="E13" s="81">
         <v>3450224900</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G13" s="78" t="s">
+      <c r="G13" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I13" s="44">
+      <c r="I13" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3127,25 +3382,25 @@
       <c r="B14" s="7">
         <v>46037</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>136270632</v>
       </c>
-      <c r="E14" s="87">
+      <c r="E14" s="81">
         <v>3450219730</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G14" s="78" t="s">
+      <c r="G14" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3156,25 +3411,25 @@
       <c r="B15" s="7">
         <v>46041</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>136343008</v>
       </c>
-      <c r="E15" s="87">
+      <c r="E15" s="81">
         <v>3450221841</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G15" s="78" t="s">
+      <c r="G15" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I15" s="44">
+      <c r="I15" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -3185,25 +3440,25 @@
       <c r="B16" s="7">
         <v>46037</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <v>136284069</v>
       </c>
-      <c r="E16" s="87">
+      <c r="E16" s="81">
         <v>3450219685</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G16" s="78" t="s">
+      <c r="G16" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3214,25 +3469,25 @@
       <c r="B17" s="7">
         <v>46044</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>136366672</v>
       </c>
-      <c r="E17" s="87">
+      <c r="E17" s="81">
         <v>3450226241</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G17" s="78" t="s">
+      <c r="G17" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="I17" s="44">
+      <c r="I17" s="43">
         <v>46044</v>
       </c>
     </row>
@@ -3243,25 +3498,25 @@
       <c r="B18" s="7">
         <v>46048</v>
       </c>
-      <c r="C18" s="56" t="s">
+      <c r="C18" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>136413290</v>
       </c>
-      <c r="E18" s="87">
+      <c r="E18" s="81">
         <v>3450230146</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="G18" s="78" t="s">
+      <c r="G18" s="72" t="s">
         <v>69</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="44">
+      <c r="I18" s="43">
         <v>46048</v>
       </c>
     </row>
@@ -3272,25 +3527,25 @@
       <c r="B19" s="7">
         <v>46048</v>
       </c>
-      <c r="C19" s="56" t="s">
+      <c r="C19" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>136413481</v>
       </c>
-      <c r="E19" s="87">
+      <c r="E19" s="81">
         <v>3450230168</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G19" s="78" t="s">
+      <c r="G19" s="72" t="s">
         <v>69</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="43">
         <v>46048</v>
       </c>
     </row>
@@ -3301,25 +3556,25 @@
       <c r="B20" s="7">
         <v>46036</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <v>136260233</v>
       </c>
-      <c r="E20" s="87">
+      <c r="E20" s="81">
         <v>3450217133</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G20" s="78" t="s">
+      <c r="G20" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I20" s="44">
+      <c r="I20" s="43">
         <v>46036</v>
       </c>
     </row>
@@ -3330,25 +3585,25 @@
       <c r="B21" s="7">
         <v>46050</v>
       </c>
-      <c r="C21" s="56" t="s">
+      <c r="C21" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="21">
         <v>136262951</v>
       </c>
-      <c r="E21" s="87">
+      <c r="E21" s="81">
         <v>3450218926</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G21" s="78" t="s">
+      <c r="G21" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="I21" s="44">
+      <c r="I21" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3359,25 +3614,25 @@
       <c r="B22" s="7">
         <v>46037</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <v>136263322</v>
       </c>
-      <c r="E22" s="87">
+      <c r="E22" s="81">
         <v>3450218981</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G22" s="78" t="s">
+      <c r="G22" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I22" s="44">
+      <c r="I22" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3388,25 +3643,25 @@
       <c r="B23" s="7">
         <v>46037</v>
       </c>
-      <c r="C23" s="56" t="s">
+      <c r="C23" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <v>136266846</v>
       </c>
-      <c r="E23" s="87">
+      <c r="E23" s="81">
         <v>3450219290</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G23" s="78" t="s">
+      <c r="G23" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="44">
+      <c r="I23" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3417,25 +3672,25 @@
       <c r="B24" s="7">
         <v>46037</v>
       </c>
-      <c r="C24" s="56" t="s">
+      <c r="C24" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <v>136273043</v>
       </c>
-      <c r="E24" s="87">
+      <c r="E24" s="81">
         <v>3450219938</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="78" t="s">
+      <c r="G24" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I24" s="44">
+      <c r="I24" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3446,25 +3701,25 @@
       <c r="B25" s="7">
         <v>46037</v>
       </c>
-      <c r="C25" s="56" t="s">
+      <c r="C25" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <v>136266045</v>
       </c>
-      <c r="E25" s="87">
+      <c r="E25" s="81">
         <v>3450219223</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="G25" s="78" t="s">
+      <c r="G25" s="72" t="s">
         <v>24</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="I25" s="44">
+      <c r="I25" s="43">
         <v>46048</v>
       </c>
     </row>
@@ -3475,25 +3730,25 @@
       <c r="B26" s="7">
         <v>46037</v>
       </c>
-      <c r="C26" s="56" t="s">
+      <c r="C26" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <v>136263610</v>
       </c>
-      <c r="E26" s="87">
+      <c r="E26" s="81">
         <v>3450219036</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G26" s="78" t="s">
+      <c r="G26" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I26" s="44">
+      <c r="I26" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3504,25 +3759,25 @@
       <c r="B27" s="7">
         <v>46037</v>
       </c>
-      <c r="C27" s="56" t="s">
+      <c r="C27" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <v>136261409</v>
       </c>
-      <c r="E27" s="87">
+      <c r="E27" s="81">
         <v>3450218739</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="G27" s="78" t="s">
+      <c r="G27" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="44">
+      <c r="I27" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3533,25 +3788,25 @@
       <c r="B28" s="7">
         <v>46054</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <v>136264032</v>
       </c>
-      <c r="E28" s="87">
+      <c r="E28" s="81">
         <v>3450219069</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="G28" s="78" t="s">
+      <c r="G28" s="72" t="s">
         <v>29</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="I28" s="44">
+      <c r="I28" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3562,25 +3817,25 @@
       <c r="B29" s="7">
         <v>46037</v>
       </c>
-      <c r="C29" s="56" t="s">
+      <c r="C29" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="21">
         <v>136274090</v>
       </c>
-      <c r="E29" s="87">
+      <c r="E29" s="81">
         <v>3450219982</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G29" s="78" t="s">
+      <c r="G29" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I29" s="44">
+      <c r="I29" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3591,25 +3846,25 @@
       <c r="B30" s="7">
         <v>46037</v>
       </c>
-      <c r="C30" s="56" t="s">
+      <c r="C30" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="21">
         <v>136270483</v>
       </c>
-      <c r="E30" s="87">
+      <c r="E30" s="81">
         <v>3450219707</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="G30" s="78" t="s">
+      <c r="G30" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I30" s="44">
+      <c r="I30" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -3620,25 +3875,25 @@
       <c r="B31" s="7">
         <v>46037</v>
       </c>
-      <c r="C31" s="56" t="s">
+      <c r="C31" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="21">
         <v>136264571</v>
       </c>
-      <c r="E31" s="87">
+      <c r="E31" s="81">
         <v>3450219113</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G31" s="78" t="s">
+      <c r="G31" s="72" t="s">
         <v>29</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="I31" s="44">
+      <c r="I31" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3649,25 +3904,25 @@
       <c r="B32" s="7">
         <v>46037</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="C32" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="21">
         <v>136264995</v>
       </c>
-      <c r="E32" s="87">
+      <c r="E32" s="81">
         <v>3450219157</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="G32" s="78" t="s">
+      <c r="G32" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="I32" s="44">
+      <c r="I32" s="43">
         <v>46041</v>
       </c>
     </row>
@@ -3678,25 +3933,25 @@
       <c r="B33" s="7">
         <v>46042</v>
       </c>
-      <c r="C33" s="56" t="s">
+      <c r="C33" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="21">
         <v>136346369</v>
       </c>
-      <c r="E33" s="87">
+      <c r="E33" s="81">
         <v>3450223337</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G33" s="78" t="s">
+      <c r="G33" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="I33" s="44">
+      <c r="I33" s="43">
         <v>46042</v>
       </c>
     </row>
@@ -3707,25 +3962,25 @@
       <c r="B34" s="7">
         <v>46036</v>
       </c>
-      <c r="C34" s="56" t="s">
+      <c r="C34" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="21">
         <v>136241606</v>
       </c>
-      <c r="E34" s="87">
+      <c r="E34" s="81">
         <v>3450217177</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G34" s="78" t="s">
+      <c r="G34" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="I34" s="44">
+      <c r="I34" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3736,25 +3991,25 @@
       <c r="B35" s="7">
         <v>46059</v>
       </c>
-      <c r="C35" s="56" t="s">
+      <c r="C35" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="21">
         <v>136241976</v>
       </c>
-      <c r="E35" s="87">
+      <c r="E35" s="81">
         <v>3450217200</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="G35" s="78" t="s">
+      <c r="G35" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="I35" s="44">
+      <c r="I35" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3765,25 +4020,25 @@
       <c r="B36" s="7">
         <v>46036</v>
       </c>
-      <c r="C36" s="56" t="s">
+      <c r="C36" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="21">
         <v>136241993</v>
       </c>
-      <c r="E36" s="87">
+      <c r="E36" s="81">
         <v>3450217221</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G36" s="78" t="s">
+      <c r="G36" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="44">
+      <c r="I36" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3794,25 +4049,25 @@
       <c r="B37" s="7">
         <v>46066</v>
       </c>
-      <c r="C37" s="56" t="s">
+      <c r="C37" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="21">
         <v>136242345</v>
       </c>
-      <c r="E37" s="87">
+      <c r="E37" s="81">
         <v>3450217254</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="G37" s="78" t="s">
+      <c r="G37" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="I37" s="44">
+      <c r="I37" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3823,25 +4078,25 @@
       <c r="B38" s="7">
         <v>46043</v>
       </c>
-      <c r="C38" s="56" t="s">
+      <c r="C38" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="21">
         <v>136346132</v>
       </c>
-      <c r="E38" s="87">
+      <c r="E38" s="81">
         <v>3450224657</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="G38" s="78" t="s">
+      <c r="G38" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="I38" s="44">
+      <c r="I38" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3852,25 +4107,25 @@
       <c r="B39" s="7">
         <v>46036</v>
       </c>
-      <c r="C39" s="56" t="s">
+      <c r="C39" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="21">
         <v>136242410</v>
       </c>
-      <c r="E39" s="87">
+      <c r="E39" s="81">
         <v>3450217276</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="G39" s="78" t="s">
+      <c r="G39" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="I39" s="44">
+      <c r="I39" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3881,25 +4136,25 @@
       <c r="B40" s="7">
         <v>46066</v>
       </c>
-      <c r="C40" s="56" t="s">
+      <c r="C40" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="21">
         <v>136242868</v>
       </c>
-      <c r="E40" s="87">
+      <c r="E40" s="81">
         <v>3450217386</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="G40" s="78" t="s">
+      <c r="G40" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I40" s="44">
+      <c r="I40" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3910,25 +4165,25 @@
       <c r="B41" s="7">
         <v>46042</v>
       </c>
-      <c r="C41" s="56" t="s">
+      <c r="C41" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="21">
         <v>136243081</v>
       </c>
-      <c r="E41" s="87">
+      <c r="E41" s="81">
         <v>3450217397</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="G41" s="78" t="s">
+      <c r="G41" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I41" s="44">
+      <c r="I41" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3939,25 +4194,25 @@
       <c r="B42" s="7">
         <v>46039</v>
       </c>
-      <c r="C42" s="56" t="s">
+      <c r="C42" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="21">
         <v>136247141</v>
       </c>
-      <c r="E42" s="87">
+      <c r="E42" s="81">
         <v>3450217727</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G42" s="78" t="s">
+      <c r="G42" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I42" s="44">
+      <c r="I42" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3968,25 +4223,25 @@
       <c r="B43" s="7">
         <v>46051</v>
       </c>
-      <c r="C43" s="56" t="s">
+      <c r="C43" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="21">
         <v>136249442</v>
       </c>
-      <c r="E43" s="87">
+      <c r="E43" s="81">
         <v>3450217958</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="G43" s="78" t="s">
+      <c r="G43" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="I43" s="44">
+      <c r="I43" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -3997,25 +4252,25 @@
       <c r="B44" s="7">
         <v>46043</v>
       </c>
-      <c r="C44" s="56" t="s">
+      <c r="C44" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="21">
         <v>136354969</v>
       </c>
-      <c r="E44" s="87">
+      <c r="E44" s="81">
         <v>3450225526</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="G44" s="78" t="s">
+      <c r="G44" s="72" t="s">
         <v>44</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="I44" s="44">
+      <c r="I44" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -4026,25 +4281,25 @@
       <c r="B45" s="7">
         <v>46037</v>
       </c>
-      <c r="C45" s="56" t="s">
+      <c r="C45" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="21">
         <v>136263225</v>
       </c>
-      <c r="E45" s="87">
+      <c r="E45" s="81">
         <v>3450218959</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="G45" s="78" t="s">
+      <c r="G45" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H45" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I45" s="44">
+      <c r="I45" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -4055,25 +4310,25 @@
       <c r="B46" s="7">
         <v>46038</v>
       </c>
-      <c r="C46" s="56" t="s">
+      <c r="C46" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="21">
         <v>136283613</v>
       </c>
-      <c r="E46" s="87">
+      <c r="E46" s="81">
         <v>3450220400</v>
       </c>
       <c r="F46" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="G46" s="78" t="s">
+      <c r="G46" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I46" s="44">
+      <c r="I46" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -4084,25 +4339,25 @@
       <c r="B47" s="7">
         <v>46038</v>
       </c>
-      <c r="C47" s="56" t="s">
+      <c r="C47" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="21">
         <v>136283757</v>
       </c>
-      <c r="E47" s="87">
+      <c r="E47" s="81">
         <v>3450220455</v>
       </c>
       <c r="F47" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="G47" s="78" t="s">
+      <c r="G47" s="72" t="s">
         <v>21</v>
       </c>
       <c r="H47" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="I47" s="44">
+      <c r="I47" s="43">
         <v>46043</v>
       </c>
     </row>
@@ -4113,25 +4368,25 @@
       <c r="B48" s="7">
         <v>46037</v>
       </c>
-      <c r="C48" s="56" t="s">
+      <c r="C48" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D48" s="22">
+      <c r="D48" s="21">
         <v>136284425</v>
       </c>
-      <c r="E48" s="87">
+      <c r="E48" s="81">
         <v>3450219014</v>
       </c>
       <c r="F48" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="G48" s="78" t="s">
+      <c r="G48" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H48" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I48" s="44">
+      <c r="I48" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -4142,25 +4397,25 @@
       <c r="B49" s="7">
         <v>46037</v>
       </c>
-      <c r="C49" s="56" t="s">
+      <c r="C49" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="21">
         <v>136284557</v>
       </c>
-      <c r="E49" s="87">
+      <c r="E49" s="81">
         <v>3450219212</v>
       </c>
       <c r="F49" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="G49" s="78" t="s">
+      <c r="G49" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H49" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I49" s="44">
+      <c r="I49" s="43">
         <v>46037</v>
       </c>
     </row>
@@ -4171,25 +4426,25 @@
       <c r="B50" s="7">
         <v>46038</v>
       </c>
-      <c r="C50" s="56" t="s">
+      <c r="C50" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="21">
         <v>136289064</v>
       </c>
-      <c r="E50" s="87">
+      <c r="E50" s="81">
         <v>3450220928</v>
       </c>
       <c r="F50" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G50" s="78" t="s">
+      <c r="G50" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H50" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I50" s="44">
+      <c r="I50" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -4200,25 +4455,25 @@
       <c r="B51" s="7">
         <v>46038</v>
       </c>
-      <c r="C51" s="56" t="s">
+      <c r="C51" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="21">
         <v>136291474</v>
       </c>
-      <c r="E51" s="87">
+      <c r="E51" s="81">
         <v>3450221093</v>
       </c>
       <c r="F51" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G51" s="78" t="s">
+      <c r="G51" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H51" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I51" s="44">
+      <c r="I51" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -4229,25 +4484,25 @@
       <c r="B52" s="7">
         <v>46038</v>
       </c>
-      <c r="C52" s="56" t="s">
+      <c r="C52" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="21">
         <v>136291832</v>
       </c>
-      <c r="E52" s="87">
+      <c r="E52" s="81">
         <v>3450221115</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="G52" s="78" t="s">
+      <c r="G52" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H52" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I52" s="44">
+      <c r="I52" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -4258,25 +4513,25 @@
       <c r="B53" s="7">
         <v>46038</v>
       </c>
-      <c r="C53" s="56" t="s">
+      <c r="C53" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="21">
         <v>136292532</v>
       </c>
-      <c r="E53" s="87">
+      <c r="E53" s="81">
         <v>3450221203</v>
       </c>
       <c r="F53" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="G53" s="78" t="s">
+      <c r="G53" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H53" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I53" s="44">
+      <c r="I53" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -4287,25 +4542,25 @@
       <c r="B54" s="7">
         <v>46038</v>
       </c>
-      <c r="C54" s="56" t="s">
+      <c r="C54" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D54" s="22">
+      <c r="D54" s="21">
         <v>136293814</v>
       </c>
-      <c r="E54" s="87">
+      <c r="E54" s="81">
         <v>3450221302</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="G54" s="78" t="s">
+      <c r="G54" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H54" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I54" s="44">
+      <c r="I54" s="43">
         <v>46038</v>
       </c>
     </row>
@@ -4316,38 +4571,38 @@
       <c r="B55" s="7">
         <v>46038</v>
       </c>
-      <c r="C55" s="56" t="s">
+      <c r="C55" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D55" s="22">
+      <c r="D55" s="21">
         <v>136294618</v>
       </c>
-      <c r="E55" s="87">
+      <c r="E55" s="81">
         <v>3450221379</v>
       </c>
       <c r="F55" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="G55" s="78" t="s">
+      <c r="G55" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H55" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I55" s="44">
+      <c r="I55" s="43">
         <v>46038</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="6"/>
       <c r="B56" s="7"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="60"/>
-      <c r="E56" s="88"/>
+      <c r="C56" s="55"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="82"/>
       <c r="F56" s="11"/>
-      <c r="G56" s="78"/>
+      <c r="G56" s="72"/>
       <c r="H56" s="12"/>
-      <c r="I56" s="44"/>
+      <c r="I56" s="43"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -4369,17 +4624,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="15.85546875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" style="16" customWidth="1"/>
     <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" style="16" customWidth="1"/>
+    <col min="5" max="5" width="30.140625" style="16" customWidth="1"/>
     <col min="6" max="6" width="30.140625" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="24" customWidth="1"/>
+    <col min="7" max="7" width="23.28515625" customWidth="1"/>
+    <col min="8" max="8" width="29.28515625" customWidth="1"/>
+    <col min="9" max="9" width="21" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -4407,7 +4663,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="27" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4415,28 +4671,28 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="60" t="s">
         <v>163</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="61" t="s">
         <v>165</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="62">
         <v>3450231554</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="63" t="s">
         <v>166</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="I2" s="44" t="s">
+      <c r="I2" s="43" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4444,461 +4700,1089 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="44"/>
+      <c r="B3" s="60">
+        <v>46041</v>
+      </c>
+      <c r="C3" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="89">
+        <v>136319087</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450222985</v>
+      </c>
+      <c r="F3" s="83" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I3" s="43">
+        <v>46049</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="44"/>
+      <c r="B4" s="60">
+        <v>46048</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4" s="89">
+        <v>136348722</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450224965</v>
+      </c>
+      <c r="F4" s="83" t="s">
+        <v>171</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" s="43">
+        <v>46048</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="49"/>
+      <c r="B5" s="60">
+        <v>46043</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="89">
+        <v>136355676</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450225636</v>
+      </c>
+      <c r="F5" s="83" t="s">
+        <v>172</v>
+      </c>
+      <c r="G5" s="84" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="I5" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="60">
+        <v>46043</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="89">
+        <v>136355567</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450225625</v>
+      </c>
+      <c r="F6" s="83" t="s">
+        <v>174</v>
+      </c>
+      <c r="G6" s="85" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="I6" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="61"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="44"/>
+      <c r="B7" s="60">
+        <v>46044</v>
+      </c>
+      <c r="C7" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="89">
+        <v>136364079</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450226065</v>
+      </c>
+      <c r="F7" s="83" t="s">
+        <v>176</v>
+      </c>
+      <c r="G7" s="85" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="I7" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="61"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="44"/>
+      <c r="B8" s="60">
+        <v>46044</v>
+      </c>
+      <c r="C8" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="89">
+        <v>136366453</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450226208</v>
+      </c>
+      <c r="F8" s="83" t="s">
+        <v>178</v>
+      </c>
+      <c r="G8" s="85" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="43">
+        <v>46049</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="61"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="60">
+        <v>46044</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D9" s="89">
+        <v>136366808</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450226285</v>
+      </c>
+      <c r="F9" s="83" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="85" t="s">
+        <v>69</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="44"/>
+      <c r="B10" s="60">
+        <v>46063</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="89">
+        <v>136368326</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450226440</v>
+      </c>
+      <c r="F10" s="83" t="s">
+        <v>180</v>
+      </c>
+      <c r="G10" s="86" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="I10" s="43">
+        <v>46049</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="44"/>
+      <c r="B11" s="60">
+        <v>46044</v>
+      </c>
+      <c r="C11" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="89">
+        <v>136367932</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450226417</v>
+      </c>
+      <c r="F11" s="83" t="s">
+        <v>181</v>
+      </c>
+      <c r="G11" s="85" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="I11" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="44"/>
+      <c r="B12" s="60">
+        <v>46044</v>
+      </c>
+      <c r="C12" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="89">
+        <v>136376326</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450227198</v>
+      </c>
+      <c r="F12" s="83" t="s">
+        <v>183</v>
+      </c>
+      <c r="G12" s="86" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I12" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="44"/>
+      <c r="B13" s="60">
+        <v>46044</v>
+      </c>
+      <c r="C13" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="89">
+        <v>136372112</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450226813</v>
+      </c>
+      <c r="F13" s="83" t="s">
+        <v>184</v>
+      </c>
+      <c r="G13" s="85" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="I13" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="61"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="44"/>
+      <c r="B14" s="60">
+        <v>46053</v>
+      </c>
+      <c r="C14" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="89">
+        <v>136374664</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450227055</v>
+      </c>
+      <c r="F14" s="83" t="s">
+        <v>186</v>
+      </c>
+      <c r="G14" s="85" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" s="43">
+        <v>46048</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="44"/>
+      <c r="B15" s="60">
+        <v>46045</v>
+      </c>
+      <c r="C15" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D15" s="89">
+        <v>136386252</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450227792</v>
+      </c>
+      <c r="F15" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="G15" s="86" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="I15" s="43">
+        <v>46045</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="44"/>
+      <c r="B16" s="60">
+        <v>46042</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" s="89">
+        <v>136304193</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450221710</v>
+      </c>
+      <c r="F16" s="83" t="s">
+        <v>189</v>
+      </c>
+      <c r="G16" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="90" t="s">
+        <v>190</v>
+      </c>
+      <c r="I16" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="44"/>
+      <c r="B17" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C17" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D17" s="89">
+        <v>136269380</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450219586</v>
+      </c>
+      <c r="F17" s="83" t="s">
+        <v>191</v>
+      </c>
+      <c r="G17" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="90" t="s">
+        <v>192</v>
+      </c>
+      <c r="I17" s="43">
+        <v>46041</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="44"/>
+      <c r="B18" s="7">
+        <v>46044</v>
+      </c>
+      <c r="C18" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D18" s="89">
+        <v>136368575</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450226461</v>
+      </c>
+      <c r="F18" s="83" t="s">
+        <v>193</v>
+      </c>
+      <c r="G18" s="85" t="s">
+        <v>44</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I18" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C19" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" s="89">
+        <v>136263250</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450218960</v>
+      </c>
+      <c r="F19" s="83" t="s">
+        <v>195</v>
+      </c>
+      <c r="G19" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="90" t="s">
+        <v>196</v>
+      </c>
+      <c r="I19" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="44"/>
+      <c r="B20" s="7">
+        <v>46067</v>
+      </c>
+      <c r="C20" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" s="89">
+        <v>136263518</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450219003</v>
+      </c>
+      <c r="F20" s="83" t="s">
+        <v>197</v>
+      </c>
+      <c r="G20" s="86" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="90" t="s">
+        <v>198</v>
+      </c>
+      <c r="I20" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="44"/>
+      <c r="B21" s="7">
+        <v>46045</v>
+      </c>
+      <c r="C21" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D21" s="89">
+        <v>136264017</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450219058</v>
+      </c>
+      <c r="F21" s="83" t="s">
+        <v>199</v>
+      </c>
+      <c r="G21" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="90" t="s">
+        <v>196</v>
+      </c>
+      <c r="I21" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="7">
+        <v>46053</v>
+      </c>
+      <c r="C22" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D22" s="89">
+        <v>136264607</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450219135</v>
+      </c>
+      <c r="F22" s="83" t="s">
+        <v>200</v>
+      </c>
+      <c r="G22" s="87" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" s="90" t="s">
+        <v>196</v>
+      </c>
+      <c r="I22" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C23" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="89">
+        <v>136259294</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450218563</v>
+      </c>
+      <c r="F23" s="83" t="s">
+        <v>201</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="90" t="s">
+        <v>202</v>
+      </c>
+      <c r="I23" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46066</v>
+      </c>
+      <c r="C24" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D24" s="89">
+        <v>136259505</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450218607</v>
+      </c>
+      <c r="F24" s="83" t="s">
+        <v>203</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="90" t="s">
+        <v>204</v>
+      </c>
+      <c r="I24" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="9"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C25" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="89">
+        <v>136260297</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450218640</v>
+      </c>
+      <c r="F25" s="83" t="s">
+        <v>205</v>
+      </c>
+      <c r="G25" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="90" t="s">
+        <v>206</v>
+      </c>
+      <c r="I25" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="9"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C26" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D26" s="89">
+        <v>136260554</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450218662</v>
+      </c>
+      <c r="F26" s="83" t="s">
+        <v>207</v>
+      </c>
+      <c r="G26" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="90" t="s">
+        <v>196</v>
+      </c>
+      <c r="I26" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="9"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46039</v>
+      </c>
+      <c r="C27" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D27" s="89">
+        <v>136262149</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450218816</v>
+      </c>
+      <c r="F27" s="83" t="s">
+        <v>208</v>
+      </c>
+      <c r="G27" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="90" t="s">
+        <v>209</v>
+      </c>
+      <c r="I27" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="9"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C28" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D28" s="89">
+        <v>136262878</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450218915</v>
+      </c>
+      <c r="F28" s="83" t="s">
+        <v>210</v>
+      </c>
+      <c r="G28" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" s="90" t="s">
+        <v>211</v>
+      </c>
+      <c r="I28" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="9"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46044</v>
+      </c>
+      <c r="C29" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="89">
+        <v>136363334</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450226000</v>
+      </c>
+      <c r="F29" s="83" t="s">
+        <v>212</v>
+      </c>
+      <c r="G29" s="88" t="s">
+        <v>24</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="I29" s="43">
+        <v>46049</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="9"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46052</v>
+      </c>
+      <c r="C30" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D30" s="89">
+        <v>136265017</v>
+      </c>
+      <c r="E30" s="17">
+        <v>3450219168</v>
+      </c>
+      <c r="F30" s="83" t="s">
+        <v>213</v>
+      </c>
+      <c r="G30" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="90" t="s">
+        <v>214</v>
+      </c>
+      <c r="I30" s="43">
+        <v>46044</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="9"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46041</v>
+      </c>
+      <c r="C31" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="89">
+        <v>136265290</v>
+      </c>
+      <c r="E31" s="17">
+        <v>3450219180</v>
+      </c>
+      <c r="F31" s="83" t="s">
+        <v>215</v>
+      </c>
+      <c r="G31" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="90" t="s">
+        <v>118</v>
+      </c>
+      <c r="I31" s="43">
+        <v>46043</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-    </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46042</v>
+      </c>
+      <c r="C32" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" s="89">
+        <v>136266581</v>
+      </c>
+      <c r="E32" s="17">
+        <v>3450219278</v>
+      </c>
+      <c r="F32" s="83" t="s">
+        <v>216</v>
+      </c>
+      <c r="G32" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="90" t="s">
+        <v>217</v>
+      </c>
+      <c r="I32" s="43">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46063</v>
+      </c>
+      <c r="C33" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D33" s="89">
+        <v>136268365</v>
+      </c>
+      <c r="E33" s="17">
+        <v>3450219454</v>
+      </c>
+      <c r="F33" s="83" t="s">
+        <v>218</v>
+      </c>
+      <c r="G33" s="88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="90" t="s">
+        <v>219</v>
+      </c>
+      <c r="I33" s="43">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46042</v>
+      </c>
+      <c r="C34" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34" s="89">
+        <v>136269775</v>
+      </c>
+      <c r="E34" s="17">
+        <v>3450219641</v>
+      </c>
+      <c r="F34" s="83" t="s">
+        <v>220</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" s="90" t="s">
+        <v>196</v>
+      </c>
+      <c r="I34" s="43">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46037</v>
+      </c>
+      <c r="C35" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" s="89">
+        <v>136268692</v>
+      </c>
+      <c r="E35" s="17">
+        <v>3450219510</v>
+      </c>
+      <c r="F35" s="83" t="s">
+        <v>221</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="90" t="s">
+        <v>222</v>
+      </c>
+      <c r="I35" s="43">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46038</v>
+      </c>
+      <c r="C36" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D36" s="89">
+        <v>136284082</v>
+      </c>
+      <c r="E36" s="17">
+        <v>3450220499</v>
+      </c>
+      <c r="F36" s="83" t="s">
+        <v>223</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="90" t="s">
+        <v>224</v>
+      </c>
+      <c r="I36" s="43">
+        <v>46043</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
+        <v>46041</v>
+      </c>
+      <c r="C37" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D37" s="89">
+        <v>136317936</v>
+      </c>
+      <c r="E37" s="17">
+        <v>3450222908</v>
+      </c>
+      <c r="F37" s="83" t="s">
+        <v>225</v>
+      </c>
+      <c r="G37" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" s="90" t="s">
+        <v>226</v>
+      </c>
+      <c r="I37" s="43">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>46044</v>
+      </c>
+      <c r="C38" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="89">
+        <v>136370920</v>
+      </c>
+      <c r="E38" s="17">
+        <v>3450226660</v>
+      </c>
+      <c r="F38" s="83" t="s">
+        <v>227</v>
+      </c>
+      <c r="G38" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="I38" s="43">
+        <v>46044</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="7">
+        <v>46044</v>
+      </c>
+      <c r="C39" s="60" t="s">
+        <v>164</v>
+      </c>
+      <c r="D39" s="89">
+        <v>136375283</v>
+      </c>
+      <c r="E39" s="17">
+        <v>3450227132</v>
+      </c>
+      <c r="F39" s="83" t="s">
+        <v>229</v>
+      </c>
+      <c r="G39" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="H39" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="I39" s="43">
+        <v>46044</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="3">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A23:A33" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G33" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+  <dataValidations count="3">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B16 C2:C39" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G32" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A22" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A39" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17 C2" xr:uid="{7AD82A11-4EC7-4EF9-95FB-52EC6839A0E7}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4953,40 +5837,40 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="8"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="27"/>
+      <c r="G2" s="26"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="25"/>
       <c r="E3" s="8"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="27"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="24"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
       <c r="E4" s="8"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="27"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -4994,12 +5878,12 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="26"/>
+      <c r="D5" s="25"/>
       <c r="E5" s="8"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="27"/>
+      <c r="G5" s="26"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -5007,12 +5891,12 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="26"/>
+      <c r="D6" s="25"/>
       <c r="E6" s="8"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="23"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
@@ -5020,12 +5904,12 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="26"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="8"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="27"/>
+      <c r="G7" s="26"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="24"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
@@ -5033,12 +5917,12 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="26"/>
+      <c r="D8" s="25"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="24"/>
+      <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
@@ -5046,12 +5930,12 @@
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="26"/>
+      <c r="D9" s="25"/>
       <c r="E9" s="8"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="27"/>
+      <c r="G9" s="26"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="24"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
@@ -5059,12 +5943,12 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="26"/>
+      <c r="D10" s="25"/>
       <c r="E10" s="8"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="24"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
@@ -5072,12 +5956,12 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="26"/>
+      <c r="D11" s="25"/>
       <c r="E11" s="8"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="27"/>
+      <c r="G11" s="26"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="24"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
@@ -5085,12 +5969,12 @@
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="26"/>
+      <c r="D12" s="25"/>
       <c r="E12" s="8"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="27"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="24"/>
+      <c r="I12" s="23"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
@@ -5098,12 +5982,12 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="26"/>
+      <c r="D13" s="25"/>
       <c r="E13" s="8"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="27"/>
+      <c r="G13" s="26"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="24"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
@@ -5111,12 +5995,12 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="26"/>
+      <c r="D14" s="25"/>
       <c r="E14" s="8"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="27"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="24"/>
+      <c r="I14" s="23"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
@@ -5124,23 +6008,23 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="26"/>
+      <c r="D15" s="25"/>
       <c r="E15" s="8"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="27"/>
+      <c r="G15" s="26"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="24"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="26"/>
+      <c r="D16" s="25"/>
       <c r="E16" s="8"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="27"/>
+      <c r="G16" s="26"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="24"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -5151,7 +6035,7 @@
       <c r="F17" s="11"/>
       <c r="G17" s="6"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="24"/>
+      <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -5162,7 +6046,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="6"/>
       <c r="H18" s="9"/>
-      <c r="I18" s="24"/>
+      <c r="I18" s="23"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
@@ -5173,7 +6057,7 @@
       <c r="F19" s="12"/>
       <c r="G19" s="6"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="23"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -5184,7 +6068,7 @@
       <c r="F20" s="14"/>
       <c r="G20" s="6"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="23"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -5603,63 +6487,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
       <c r="G2" s="19"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="24"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
       <c r="G3" s="19"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="33"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
       <c r="G4" s="19"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="24"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
       <c r="G5" s="19"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="24"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="20"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="24"/>
+      <c r="I6" s="23"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -6186,7 +7070,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="38" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -6198,232 +7082,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="24"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="23"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="24"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="24"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="23"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="24"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="23"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="24"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="23"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="24"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="23"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="24"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="34"/>
-      <c r="I9" s="24"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="24"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="24"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="24"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="23"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="24"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="24"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="23"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="24"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="24"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="24"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="23"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="24"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="23"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="28"/>
       <c r="H19" s="9"/>
-      <c r="I19" s="24"/>
+      <c r="I19" s="23"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -6432,9 +7316,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="29"/>
+      <c r="G20" s="28"/>
       <c r="H20" s="9"/>
-      <c r="I20" s="24"/>
+      <c r="I20" s="23"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -6443,9 +7327,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="29"/>
+      <c r="G21" s="28"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="24"/>
+      <c r="I21" s="23"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -6454,9 +7338,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="29"/>
+      <c r="G22" s="28"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="24"/>
+      <c r="I22" s="23"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -6465,9 +7349,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="29"/>
+      <c r="G23" s="28"/>
       <c r="H23" s="9"/>
-      <c r="I23" s="24"/>
+      <c r="I23" s="23"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -6476,9 +7360,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="29"/>
+      <c r="G24" s="28"/>
       <c r="H24" s="9"/>
-      <c r="I24" s="24"/>
+      <c r="I24" s="23"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -6489,7 +7373,7 @@
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
-      <c r="I25" s="24"/>
+      <c r="I25" s="23"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -6500,7 +7384,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
-      <c r="I26" s="24"/>
+      <c r="I26" s="23"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -6511,7 +7395,7 @@
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
       <c r="H27" s="9"/>
-      <c r="I27" s="24"/>
+      <c r="I27" s="23"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -6522,7 +7406,7 @@
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
       <c r="H28" s="9"/>
-      <c r="I28" s="24"/>
+      <c r="I28" s="23"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -6533,7 +7417,7 @@
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
       <c r="H29" s="9"/>
-      <c r="I29" s="24"/>
+      <c r="I29" s="23"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -6544,7 +7428,7 @@
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="24"/>
+      <c r="I30" s="23"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -6555,7 +7439,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="24"/>
+      <c r="I31" s="23"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -6566,7 +7450,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
       <c r="H32" s="9"/>
-      <c r="I32" s="24"/>
+      <c r="I32" s="23"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -6577,7 +7461,7 @@
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
       <c r="H33" s="9"/>
-      <c r="I33" s="24"/>
+      <c r="I33" s="23"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
@@ -6588,7 +7472,7 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="24"/>
+      <c r="I34" s="23"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -6599,7 +7483,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="24"/>
+      <c r="I35" s="23"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -6877,10 +7761,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="70" t="s">
+      <c r="H1" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="51" t="s">
+      <c r="I1" s="50" t="s">
         <v>8</v>
       </c>
     </row>
@@ -6889,232 +7773,232 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="18"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="44"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="44"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="43"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="18"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="44"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="43"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="44"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="43"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="22"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="21"/>
       <c r="E6" s="17"/>
       <c r="F6" s="18"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="44"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="43"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="22"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="21"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="44"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="43"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="22"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="17"/>
       <c r="F8" s="18"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="44"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="43"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="22"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="21"/>
       <c r="E9" s="17"/>
       <c r="F9" s="18"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="44"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="43"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="22"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="17"/>
       <c r="F10" s="18"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="44"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="43"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="22"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="21"/>
       <c r="E11" s="17"/>
       <c r="F11" s="18"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="44"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="43"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="22"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="17"/>
       <c r="F12" s="18"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="71"/>
-      <c r="I12" s="44"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="43"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="22"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="21"/>
       <c r="E13" s="17"/>
       <c r="F13" s="18"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="44"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="43"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="22"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="17"/>
       <c r="F14" s="18"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="71"/>
-      <c r="I14" s="44"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="43"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="22"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="21"/>
       <c r="E15" s="17"/>
       <c r="F15" s="18"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="44"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="22"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="21"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="71"/>
-      <c r="I16" s="44"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="65"/>
+      <c r="I16" s="43"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="22"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="21"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="44"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="65"/>
+      <c r="I17" s="43"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="22"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="21"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="71"/>
-      <c r="I18" s="44"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="43"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="44"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="43"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
@@ -7123,9 +8007,9 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="44"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="43"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
@@ -7134,9 +8018,9 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="44"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="43"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
@@ -7145,9 +8029,9 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="48"/>
-      <c r="I22" s="44"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="43"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
@@ -7156,9 +8040,9 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="44"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="43"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
@@ -7167,9 +8051,9 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="44"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="43"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
@@ -7179,8 +8063,8 @@
       <c r="E25" s="8"/>
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="44"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="43"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -7190,8 +8074,8 @@
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="44"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="43"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -7201,8 +8085,8 @@
       <c r="E27" s="8"/>
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="44"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="43"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
@@ -7212,8 +8096,8 @@
       <c r="E28" s="8"/>
       <c r="F28" s="9"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="44"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="43"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
@@ -7223,8 +8107,8 @@
       <c r="E29" s="8"/>
       <c r="F29" s="9"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="44"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="43"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
@@ -7234,8 +8118,8 @@
       <c r="E30" s="8"/>
       <c r="F30" s="9"/>
       <c r="G30" s="6"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="44"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="43"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
@@ -7245,8 +8129,8 @@
       <c r="E31" s="8"/>
       <c r="F31" s="9"/>
       <c r="G31" s="6"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="44"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="43"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
@@ -7256,8 +8140,8 @@
       <c r="E32" s="8"/>
       <c r="F32" s="9"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="44"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="43"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
@@ -7267,8 +8151,8 @@
       <c r="E33" s="8"/>
       <c r="F33" s="9"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="44"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="43"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -7298,65 +8182,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-540084</_dlc_DocId>
@@ -7399,7 +8224,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="45" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="06364c42bcbf61016b6bd5e32d4d0782">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="199c6c2eefa6ec2f672a95412cfea747" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7783,18 +8608,77 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68138E73-25FB-4FFB-81FF-985AB735421F}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68138E73-25FB-4FFB-81FF-985AB735421F}"/>
 </file>